--- a/tests/__snapshots__/table.xlsx
+++ b/tests/__snapshots__/table.xlsx
@@ -573,7 +573,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2">
-        <v>45875.80224571651</v>
+        <v>46167.0074624647</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="100" customHeight="1">
@@ -587,7 +587,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2">
-        <v>45875.80224571656</v>
+        <v>46167.00746246475</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="100" customHeight="1">
@@ -601,7 +601,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="2">
-        <v>45875.80224571659</v>
+        <v>46167.00746246477</v>
       </c>
     </row>
   </sheetData>

--- a/tests/__snapshots__/table.xlsx
+++ b/tests/__snapshots__/table.xlsx
@@ -573,7 +573,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2">
-        <v>46167.0074624647</v>
+        <v>46167.3796783249</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="100" customHeight="1">
@@ -587,7 +587,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2">
-        <v>46167.00746246475</v>
+        <v>46167.37967832496</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="100" customHeight="1">
@@ -601,7 +601,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="2">
-        <v>46167.00746246477</v>
+        <v>46167.37967832498</v>
       </c>
     </row>
   </sheetData>
